--- a/downloads/smolov-jr-template.xlsx
+++ b/downloads/smolov-jr-template.xlsx
@@ -676,7 +676,7 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -688,7 +688,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Add 5-10 lb (2.5-5 kg) to your week 1 weight.</t>
+          <t>Week 1 weight plus about 10 lb (5 kg). The % here does that for a 315 lb max.</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -727,7 +727,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Add 5-10 lb (2.5-5 kg) to your week 1 weight.</t>
+          <t>Week 1 weight plus about 10 lb (5 kg). The % here does that for a 315 lb max.</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -766,7 +766,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Add 5-10 lb (2.5-5 kg) to your week 1 weight.</t>
+          <t>Week 1 weight plus about 10 lb (5 kg). The % here does that for a 315 lb max.</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -805,7 +805,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Add 5-10 lb (2.5-5 kg) to your week 1 weight.</t>
+          <t>Week 1 weight plus about 10 lb (5 kg). The % here does that for a 315 lb max.</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -844,7 +844,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Add 10-20 lb (5-10 kg) to your week 1 weight.</t>
+          <t>Week 1 weight plus about 20 lb (10 kg). The % here does that for a 315 lb max.</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -883,7 +883,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Add 10-20 lb (5-10 kg) to your week 1 weight.</t>
+          <t>Week 1 weight plus about 20 lb (10 kg). The % here does that for a 315 lb max.</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -922,7 +922,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Add 10-20 lb (5-10 kg) to your week 1 weight.</t>
+          <t>Week 1 weight plus about 20 lb (10 kg). The % here does that for a 315 lb max.</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -961,7 +961,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Add 10-20 lb (5-10 kg) to your week 1 weight.</t>
+          <t>Week 1 weight plus about 20 lb (10 kg). The % here does that for a 315 lb max.</t>
         </is>
       </c>
     </row>
